--- a/server/api/src/main/resources/template/卷王题库导入模板.xlsx
+++ b/server/api/src/main/resources/template/卷王题库导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="14640"/>
+    <workbookView windowWidth="20460" windowHeight="14500"/>
   </bookViews>
   <sheets>
     <sheet name="单选题" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="41">
   <si>
     <t>序号</t>
   </si>
@@ -136,9 +136,6 @@
   </si>
   <si>
     <t>简单 语文</t>
-  </si>
-  <si>
-    <t>å</t>
   </si>
   <si>
     <t>水浒传</t>
@@ -1175,8 +1172,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.8" outlineLevelRow="3"/>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.8" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="9.125" style="2"/>
     <col min="2" max="2" width="32.875" style="2" customWidth="1"/>
@@ -1269,11 +1266,6 @@
       </c>
       <c r="N2" s="2" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="4" ht="17" spans="5:5">
-      <c r="E4" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1362,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>20</v>
@@ -1377,7 +1369,7 @@
         <v>2.5</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>22</v>
@@ -1437,13 +1429,13 @@
         <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>20</v>
@@ -1452,7 +1444,7 @@
         <v>2.5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>22</v>
@@ -1489,34 +1481,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>13</v>
@@ -1527,19 +1519,19 @@
         <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>20</v>
@@ -1600,7 +1592,7 @@
         <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>20</v>
